--- a/docs/Työajan seuranta Juha.xlsx
+++ b/docs/Työajan seuranta Juha.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juhaj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1F2BB69-D199-49CE-8D49-87C9B061D974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5259D7C6-95DD-4E5F-BF85-67C6D89DCC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11835" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
+    <workbookView xWindow="2370" yWindow="1335" windowWidth="21600" windowHeight="11835" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Juha Jermalainen" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Ryhmä:</t>
   </si>
@@ -158,9 +157,6 @@
     <t>ER-kaavion päivitys ja siirto docs-kansioon</t>
   </si>
   <si>
-    <t>Palaverit</t>
-  </si>
-  <si>
     <t>Hakusivun suodattimet valmiiksi (20 tulosta/sivu)
 Genre-, vuosi- ja kielisuodattimet omaksi SearchFilters-komponentiksi
 PR-katselmoinnin korjaukset: jaettu API base URL, vuosisuodatus palvelinpäähän, kielisyötteen virheilmoitukset
@@ -169,13 +165,16 @@
 Kirjautumis-popupin ensimmäinen versio</t>
   </si>
   <si>
-    <t>PR tarkistukset</t>
-  </si>
-  <si>
     <t>24.9.</t>
   </si>
   <si>
-    <t>moviedetails</t>
+    <t>Leffan tietosivun suunnittelu ja ensimmäinen versio
+Rajapintojen kartoitus ja linkitysten järjestely
+PR#93 tarkastus</t>
+  </si>
+  <si>
+    <t>Palaverit 
+(koko ajalta)</t>
   </si>
 </sst>
 </file>
@@ -211,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -229,6 +228,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normaali" xfId="0" builtinId="0"/>
@@ -543,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CCCA3CA-2A17-42EC-86E5-CF5FE2A8D439}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -581,8 +583,8 @@
       <c r="C3" s="5">
         <v>1</v>
       </c>
-      <c r="D3" t="s">
-        <v>31</v>
+      <c r="D3" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="E3" s="6">
         <v>8</v>
@@ -598,9 +600,7 @@
       <c r="C4" s="5">
         <v>3</v>
       </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
+      <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -651,7 +651,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" s="5">
         <v>9.5</v>
@@ -734,20 +734,69 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="2">
-        <v>3.75</v>
+        <v>33</v>
+      </c>
+      <c r="C17" s="5">
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
+      <c r="C18" s="6"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C19" s="6"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C20" s="6"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C21" s="6"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C22" s="6"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C23" s="6"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C24" s="6"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C25" s="6"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C26" s="6"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C27" s="6"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C28" s="6"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C29" s="6"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C30" s="6"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C31" s="6"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C32" s="6"/>
+    </row>
+    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C35" s="6">
+        <f>SUM(C3:C34,E4,E3)</f>
+        <v>78.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -756,6 +805,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="44038759-07ae-40d4-bc3d-7c9fb0b3775b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009BAF6AFB37B6774A9122C6036818BC92" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c611cd0fe7e35dfe638a44e659100205">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="44038759-07ae-40d4-bc3d-7c9fb0b3775b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="36a43d4c38ea7f7b42b5de64d2c1c906" ns3:_="">
     <xsd:import namespace="44038759-07ae-40d4-bc3d-7c9fb0b3775b"/>
@@ -935,24 +1001,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3DBD177-6275-4D31-B82C-61F9284D9B7B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="44038759-07ae-40d4-bc3d-7c9fb0b3775b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="44038759-07ae-40d4-bc3d-7c9fb0b3775b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28C42445-4535-4827-89B5-92D7D04A90E8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B52374CD-1656-483C-BC7A-A879F7105755}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -970,24 +1037,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28C42445-4535-4827-89B5-92D7D04A90E8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3DBD177-6275-4D31-B82C-61F9284D9B7B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="44038759-07ae-40d4-bc3d-7c9fb0b3775b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{9f9ce49a-5101-4aa3-8c75-0d5935ad6525}" enabled="0" method="" siteId="{9f9ce49a-5101-4aa3-8c75-0d5935ad6525}" removed="1"/>

--- a/docs/Työajan seuranta Juha.xlsx
+++ b/docs/Työajan seuranta Juha.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juhaj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5259D7C6-95DD-4E5F-BF85-67C6D89DCC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1863FF0C-C6B9-46DE-A46E-DC392FF36B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2370" yWindow="1335" windowWidth="21600" windowHeight="11835" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11835" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Juha Jermalainen" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Ryhmä:</t>
   </si>
@@ -168,13 +168,29 @@
     <t>24.9.</t>
   </si>
   <si>
+    <t>Palaverit 
+(koko ajalta)</t>
+  </si>
+  <si>
     <t>Leffan tietosivun suunnittelu ja ensimmäinen versio
 Rajapintojen kartoitus ja linkitysten järjestely
-PR#93 tarkastus</t>
-  </si>
-  <si>
-    <t>Palaverit 
-(koko ajalta)</t>
+PR#93 tarkastus
+pr#95 tarkastus</t>
+  </si>
+  <si>
+    <t>Leffan tietosivun kommentoidut korjaukset
+Profiili sivun kommentoidut korjaukset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviews sivujen teko 
+PR#97 tarkastus
+</t>
+  </si>
+  <si>
+    <t>PR#98 tarkastus</t>
+  </si>
+  <si>
+    <t>Group sivuston teko</t>
   </si>
 </sst>
 </file>
@@ -210,19 +226,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -230,6 +240,9 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -574,228 +587,266 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="3">
         <v>1</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="3">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="C17" s="3">
         <v>12</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="5">
-        <v>3</v>
-      </c>
-      <c r="E4" s="6"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    </row>
+    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>46291</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>46292</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="5">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>46293</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>46294</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="3">
         <v>7</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="5">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="5">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="6"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C19" s="6"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C20" s="6"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C21" s="6"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C22" s="6"/>
+      <c r="A22" s="6"/>
+      <c r="C22" s="3"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C23" s="6"/>
+      <c r="A23" s="6"/>
+      <c r="C23" s="3"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C24" s="6"/>
+      <c r="A24" s="6"/>
+      <c r="C24" s="3"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C25" s="6"/>
+      <c r="A25" s="6"/>
+      <c r="C25" s="3"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C26" s="6"/>
+      <c r="A26" s="6"/>
+      <c r="C26" s="3"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C27" s="6"/>
+      <c r="A27" s="6"/>
+      <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C28" s="6"/>
+      <c r="A28" s="6"/>
+      <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C29" s="6"/>
+      <c r="A29" s="6"/>
+      <c r="C29" s="4"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C30" s="6"/>
+      <c r="C30" s="4"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C31" s="6"/>
+      <c r="C31" s="4"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C32" s="6"/>
+      <c r="C32" s="4"/>
     </row>
     <row r="35" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C35" s="6">
+      <c r="C35" s="4">
         <f>SUM(C3:C34,E4,E3)</f>
-        <v>78.5</v>
+        <v>93.5</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Työajan seuranta Juha.xlsx
+++ b/docs/Työajan seuranta Juha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juhaj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1863FF0C-C6B9-46DE-A46E-DC392FF36B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCDC6B7-761A-4EE5-B4DC-0022AAA1E4CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11835" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Ryhmä:</t>
   </si>
@@ -191,6 +191,18 @@
   </si>
   <si>
     <t>Group sivuston teko</t>
+  </si>
+  <si>
+    <t>1.-2.10.2026</t>
+  </si>
+  <si>
+    <t>Recommendatins lisäosa teko
+PR#107 tarkistus
+PR#109 tarkistus</t>
+  </si>
+  <si>
+    <t>Arvostelujen tähtimerkkintöjen yhdistäminen
+PR#104 tarkistus</t>
   </si>
 </sst>
 </file>
@@ -226,7 +238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -242,6 +254,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -561,14 +576,14 @@
   <dimension ref="A1:E35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.140625" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="93.7109375" customWidth="1"/>
     <col min="3" max="3" width="13.28515625" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -576,7 +591,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -802,13 +817,27 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="6"/>
-      <c r="C22" s="3"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
-      <c r="C23" s="3"/>
+    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>46295</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="3">
+        <v>11</v>
+      </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
@@ -835,6 +864,7 @@
       <c r="C29" s="4"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="7"/>
       <c r="C30" s="4"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -846,7 +876,7 @@
     <row r="35" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C35" s="4">
         <f>SUM(C3:C34,E4,E3)</f>
-        <v>93.5</v>
+        <v>112.5</v>
       </c>
     </row>
   </sheetData>
@@ -864,15 +894,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009BAF6AFB37B6774A9122C6036818BC92" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c611cd0fe7e35dfe638a44e659100205">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="44038759-07ae-40d4-bc3d-7c9fb0b3775b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="36a43d4c38ea7f7b42b5de64d2c1c906" ns3:_="">
     <xsd:import namespace="44038759-07ae-40d4-bc3d-7c9fb0b3775b"/>
@@ -1052,6 +1073,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3DBD177-6275-4D31-B82C-61F9284D9B7B}">
   <ds:schemaRefs>
@@ -1063,14 +1093,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28C42445-4535-4827-89B5-92D7D04A90E8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B52374CD-1656-483C-BC7A-A879F7105755}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1088,6 +1110,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28C42445-4535-4827-89B5-92D7D04A90E8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{9f9ce49a-5101-4aa3-8c75-0d5935ad6525}" enabled="0" method="" siteId="{9f9ce49a-5101-4aa3-8c75-0d5935ad6525}" removed="1"/>

--- a/docs/Työajan seuranta Juha.xlsx
+++ b/docs/Työajan seuranta Juha.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juhaj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCDC6B7-761A-4EE5-B4DC-0022AAA1E4CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8202194-B748-4499-B335-7ED13ACEDB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11835" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>Ryhmä:</t>
   </si>
@@ -48,24 +48,6 @@
   </si>
   <si>
     <t>Aika</t>
-  </si>
-  <si>
-    <t>7.9.</t>
-  </si>
-  <si>
-    <t>8.9.</t>
-  </si>
-  <si>
-    <t>14.9.</t>
-  </si>
-  <si>
-    <t>15.9.</t>
-  </si>
-  <si>
-    <t>17.9.</t>
-  </si>
-  <si>
-    <t>18.9.</t>
   </si>
   <si>
     <t>24.8.</t>
@@ -75,11 +57,24 @@
 Gitin ja GitHub-työnkulun opettelua</t>
   </si>
   <si>
+    <t>Palaverit 
+(koko ajalta)</t>
+  </si>
+  <si>
     <t>6.9.</t>
   </si>
   <si>
     <t>Tietokannan ER-kaavion suunnittelu ja piirtäminen
 Tietokantamallinnuksen kertausta (relaatiot, avaimet)</t>
+  </si>
+  <si>
+    <t>7.9.</t>
+  </si>
+  <si>
+    <t>ER-kaavion päivitys ja siirto docs-kansioon</t>
+  </si>
+  <si>
+    <t>8.9.</t>
   </si>
   <si>
     <t>Palaveri: Product Backlogin featureiden ja sub-issueiden luonti, priorisointi ja työmääräarviointi
@@ -105,6 +100,20 @@
 PR #73 (UiSearch) katselmointi ja merge</t>
   </si>
   <si>
+    <t>14.9.</t>
+  </si>
+  <si>
+    <t>Hakusivun suodattimet valmiiksi (20 tulosta/sivu)
+Genre-, vuosi- ja kielisuodattimet omaksi SearchFilters-komponentiksi
+PR-katselmoinnin korjaukset: jaettu API base URL, vuosisuodatus palvelinpäähän, kielisyötteen virheilmoitukset
+Theaters-näkymän refaktorointi käyttämään SearchFilters-komponenttia
+Home-näkymän genrebugin korjaus
+Kirjautumis-popupin ensimmäinen versio</t>
+  </si>
+  <si>
+    <t>15.9.</t>
+  </si>
+  <si>
     <t>UI 2.0: väripaletti, fontit ja sivujen uudelleentyylittely
 Login-popupin pilkkominen Modal- ja LoginForm-komponenteiksi
 Kirjautumis- ja rekisteröitymislomakkeet vaihdettavaan auth-popupiin
@@ -118,6 +127,9 @@
     <t>Placeholder-komponentti tulevia sivuja varten ja navbarin otsikkotyylit
 Haarojen yhdistäminen main-haaraan
 PR #81 (Registration) katselmointi ja merge</t>
+  </si>
+  <si>
+    <t>17.9.</t>
   </si>
   <si>
     <t>Käyttäjäprofiilin käyttöliittymä (Profile-näkymä ja tyylit)
@@ -128,6 +140,9 @@
 PR #83 (LogAuth) katselmointi ja merge</t>
   </si>
   <si>
+    <t>18.9.</t>
+  </si>
+  <si>
     <t>Käyttäjätilin poiston käyttöliittymä (DeleteForm-komponentti, Modal-integraatio, Profile-näkymä)
 PR #85 (test/registration-api) katselmointi ja merge</t>
   </si>
@@ -154,22 +169,7 @@
 Seedauksen ja testidatan hallinnan opettelua</t>
   </si>
   <si>
-    <t>ER-kaavion päivitys ja siirto docs-kansioon</t>
-  </si>
-  <si>
-    <t>Hakusivun suodattimet valmiiksi (20 tulosta/sivu)
-Genre-, vuosi- ja kielisuodattimet omaksi SearchFilters-komponentiksi
-PR-katselmoinnin korjaukset: jaettu API base URL, vuosisuodatus palvelinpäähän, kielisyötteen virheilmoitukset
-Theaters-näkymän refaktorointi käyttämään SearchFilters-komponenttia
-Home-näkymän genrebugin korjaus
-Kirjautumis-popupin ensimmäinen versio</t>
-  </si>
-  <si>
     <t>24.9.</t>
-  </si>
-  <si>
-    <t>Palaverit 
-(koko ajalta)</t>
   </si>
   <si>
     <t>Leffan tietosivun suunnittelu ja ensimmäinen versio
@@ -193,6 +193,10 @@
     <t>Group sivuston teko</t>
   </si>
   <si>
+    <t>Arvostelujen tähtimerkkintöjen yhdistäminen
+PR#104 tarkistus</t>
+  </si>
+  <si>
     <t>1.-2.10.2026</t>
   </si>
   <si>
@@ -201,21 +205,72 @@
 PR#109 tarkistus</t>
   </si>
   <si>
-    <t>Arvostelujen tähtimerkkintöjen yhdistäminen
-PR#104 tarkistus</t>
+    <t>3.10.2026</t>
+  </si>
+  <si>
+    <t>PR#111 tarkistus</t>
+  </si>
+  <si>
+    <t>1,00</t>
+  </si>
+  <si>
+    <t>5.10.2026</t>
+  </si>
+  <si>
+    <t>PR#112 tarkistus</t>
+  </si>
+  <si>
+    <t>1,50</t>
+  </si>
+  <si>
+    <t>6.10.2026</t>
+  </si>
+  <si>
+    <t>Navbarin muokkaus mobiiliin sopivaksi
+Värikontrasti- ja saavutettavuuskorjaukset (WAVE)</t>
+  </si>
+  <si>
+    <t>5,00</t>
+  </si>
+  <si>
+    <t>8.10.2026</t>
+  </si>
+  <si>
+    <t>PR#115 tarkistus</t>
+  </si>
+  <si>
+    <t>2,00</t>
+  </si>
+  <si>
+    <t>9.10.2026</t>
+  </si>
+  <si>
+    <t>Oman PR#117 muokkaus ja uudelleen jako</t>
+  </si>
+  <si>
+    <t>0,50</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="d\.m\.yy;@"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -238,7 +293,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -253,12 +308,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normaali" xfId="0" builtinId="0"/>
@@ -277,9 +337,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022 -teema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -317,7 +377,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -423,7 +483,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -565,7 +625,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -574,7 +634,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CCCA3CA-2A17-42EC-86E5-CF5FE2A8D439}">
   <dimension ref="A1:E35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="93.7109375" customWidth="1"/>
@@ -582,16 +642,16 @@
     <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -601,170 +661,170 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>10</v>
+    <row r="3" spans="1:5" ht="30">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3">
         <v>1</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="E3" s="4">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>12</v>
+    <row r="4" spans="1:5" ht="30">
+      <c r="A4" s="9" t="s">
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3">
         <v>3</v>
       </c>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>4</v>
+    <row r="5" spans="1:5">
+      <c r="A5" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>5</v>
+    <row r="6" spans="1:5" ht="45">
+      <c r="A6" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>15</v>
+    <row r="7" spans="1:5" ht="75">
+      <c r="A7" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>17</v>
+    <row r="8" spans="1:5" ht="45">
+      <c r="A8" s="9" t="s">
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>6</v>
+    <row r="9" spans="1:5" ht="105">
+      <c r="A9" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3">
         <v>9.5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>7</v>
+    <row r="10" spans="1:5" ht="75">
+      <c r="A10" s="9" t="s">
+        <v>19</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3">
         <v>9.5</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>20</v>
+    <row r="11" spans="1:5" ht="45">
+      <c r="A11" s="9" t="s">
+        <v>21</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>8</v>
+    <row r="12" spans="1:5" ht="90">
+      <c r="A12" s="9" t="s">
+        <v>23</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C12" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>9</v>
+    <row r="13" spans="1:5" ht="30">
+      <c r="A13" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C13" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>24</v>
+    <row r="14" spans="1:5">
+      <c r="A14" s="9" t="s">
+        <v>27</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>26</v>
+    <row r="15" spans="1:5" ht="45">
+      <c r="A15" s="9" t="s">
+        <v>29</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C15" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>28</v>
+    <row r="16" spans="1:5" ht="45">
+      <c r="A16" s="9" t="s">
+        <v>31</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>32</v>
+    <row r="17" spans="1:3" ht="60">
+      <c r="A17" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>34</v>
@@ -773,8 +833,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+    <row r="18" spans="1:3" ht="30">
+      <c r="A18" s="9">
         <v>46291</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -784,8 +844,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+    <row r="19" spans="1:3" ht="45">
+      <c r="A19" s="9">
         <v>46292</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -795,8 +855,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+    <row r="20" spans="1:3">
+      <c r="A20" s="9">
         <v>46293</v>
       </c>
       <c r="B20" t="s">
@@ -806,8 +866,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+    <row r="21" spans="1:3">
+      <c r="A21" s="9">
         <v>46294</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -817,65 +877,100 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+    <row r="22" spans="1:3" ht="30">
+      <c r="A22" s="9">
         <v>46295</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C22" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>39</v>
+    <row r="23" spans="1:3" ht="45">
+      <c r="A23" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C23" s="3">
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="6"/>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="6"/>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="6"/>
-      <c r="C26" s="3"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="6"/>
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="6"/>
-      <c r="C28" s="3"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="6"/>
+    <row r="24" spans="1:3">
+      <c r="A24" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="30.75">
+      <c r="A26" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="9"/>
       <c r="C29" s="4"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
+    <row r="30" spans="1:3">
+      <c r="A30" s="6"/>
       <c r="C30" s="4"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="C31" s="4"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="C32" s="4"/>
     </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:3">
       <c r="C35" s="4">
-        <f>SUM(C3:C34,E4,E3)</f>
+        <f>SUM(C3:C32,E3)</f>
         <v>112.5</v>
       </c>
     </row>
@@ -886,6 +981,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_activity xmlns="44038759-07ae-40d4-bc3d-7c9fb0b3775b" xsi:nil="true"/>
@@ -893,7 +997,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009BAF6AFB37B6774A9122C6036818BC92" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c611cd0fe7e35dfe638a44e659100205">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="44038759-07ae-40d4-bc3d-7c9fb0b3775b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="36a43d4c38ea7f7b42b5de64d2c1c906" ns3:_="">
     <xsd:import namespace="44038759-07ae-40d4-bc3d-7c9fb0b3775b"/>
@@ -1073,49 +1177,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3DBD177-6275-4D31-B82C-61F9284D9B7B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="44038759-07ae-40d4-bc3d-7c9fb0b3775b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28C42445-4535-4827-89B5-92D7D04A90E8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B52374CD-1656-483C-BC7A-A879F7105755}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="44038759-07ae-40d4-bc3d-7c9fb0b3775b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3DBD177-6275-4D31-B82C-61F9284D9B7B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28C42445-4535-4827-89B5-92D7D04A90E8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B52374CD-1656-483C-BC7A-A879F7105755}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
